--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure | Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort)</t>
+    <t>Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort).
+French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -666,42 +667,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.3515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="16.6640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="14.375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="17.60546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="15.18359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,8 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort).
-French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure</t>
+    <t>French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure | Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort)</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -115,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -667,42 +666,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.41796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="16.41796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.03515625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="11.3515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="14.375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="16.6640625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="15.18359375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="17.60546875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-level-of-exertion.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure | Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort)</t>
+    <t>Extension française définie dans le contexte du profil Vital Signs Resprate. Cette extension permet de préciser le niveau d'exercice du patient durant la mesure de la fréquence respiratoire (au repos, pendant l'effort, après l'effort).
+French extension defined in the context of the Vital Signs Resprate profile. This extension is used to define the level of exertion ( at rest, during exertion, post exertion) during the respiratory rate measure</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -666,42 +667,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.3515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="16.6640625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="14.375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="14.21484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="12.26171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="19.80078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="17.60546875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.4453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="17.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="15.18359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.6796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="19.5625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
